--- a/output/upload/S00026_2207_제로백H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2207_제로백H종신보험_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2207A03</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22073</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1390,11 +1410,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2207A03</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22073</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1476,11 +1516,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2207A03</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22073</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1562,11 +1622,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2207A03</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22073</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1648,32 +1728,88 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2207A03</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22073</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
+      <c r="J11" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="6" t="n"/>
+      <c r="O11" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R11" s="6" t="n"/>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
-      <c r="X11" s="6" t="n"/>
-      <c r="Y11" s="6" t="n"/>
-      <c r="Z11" s="6" t="n"/>
-      <c r="AA11" s="6" t="n"/>
+      <c r="X11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z11" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA11" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB11" s="6" t="n"/>
       <c r="AC11" s="6" t="n"/>
       <c r="AD11" s="6" t="n"/>
@@ -1698,32 +1834,88 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2207A03</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>22073</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
+      <c r="J12" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n"/>
-      <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="6" t="n"/>
+      <c r="O12" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R12" s="6" t="n"/>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
-      <c r="X12" s="6" t="n"/>
-      <c r="Y12" s="6" t="n"/>
-      <c r="Z12" s="6" t="n"/>
-      <c r="AA12" s="6" t="n"/>
+      <c r="X12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z12" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA12" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>
       <c r="AD12" s="6" t="n"/>
@@ -1748,32 +1940,88 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2207A03</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>22073</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n"/>
+      <c r="O13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n"/>
-      <c r="Y13" s="6" t="n"/>
-      <c r="Z13" s="6" t="n"/>
-      <c r="AA13" s="6" t="n"/>
+      <c r="X13" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z13" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA13" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
       <c r="AD13" s="6" t="n"/>
@@ -1798,32 +2046,88 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2207A03</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>22073</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
-      <c r="Q14" s="6" t="n"/>
+      <c r="O14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n"/>
-      <c r="Y14" s="6" t="n"/>
-      <c r="Z14" s="6" t="n"/>
-      <c r="AA14" s="6" t="n"/>
+      <c r="X14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z14" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA14" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
       <c r="AD14" s="6" t="n"/>

--- a/output/upload/S00026_2207_제로백H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2207_제로백H종신보험_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>2207003</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>2207003</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>2207003</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>2207003</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>2207003</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>2207003</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>2207003</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>2207003</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">

--- a/output/upload/S00026_2207_제로백H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2207_제로백H종신보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV22"/>
+  <dimension ref="A1:AV38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2152,32 +2152,88 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2207A04</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>2207004</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
+      <c r="J15" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="6" t="n"/>
+      <c r="O15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
-      <c r="X15" s="6" t="n"/>
-      <c r="Y15" s="6" t="n"/>
-      <c r="Z15" s="6" t="n"/>
-      <c r="AA15" s="6" t="n"/>
+      <c r="X15" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y15" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA15" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
       <c r="AD15" s="6" t="n"/>
@@ -2202,32 +2258,88 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2207A04</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>2207004</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
+      <c r="J16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="6" t="n"/>
+      <c r="O16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
-      <c r="X16" s="6" t="n"/>
-      <c r="Y16" s="6" t="n"/>
-      <c r="Z16" s="6" t="n"/>
-      <c r="AA16" s="6" t="n"/>
+      <c r="X16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z16" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA16" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
       <c r="AD16" s="6" t="n"/>
@@ -2252,32 +2364,88 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2207A04</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2207004</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
+      <c r="J17" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
-      <c r="Q17" s="6" t="n"/>
+      <c r="O17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n"/>
-      <c r="Y17" s="6" t="n"/>
-      <c r="Z17" s="6" t="n"/>
-      <c r="AA17" s="6" t="n"/>
+      <c r="X17" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y17" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z17" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA17" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB17" s="6" t="n"/>
       <c r="AC17" s="6" t="n"/>
       <c r="AD17" s="6" t="n"/>
@@ -2302,32 +2470,88 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2207A04</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>2207004</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
+      <c r="J18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="6" t="n"/>
+      <c r="O18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
-      <c r="X18" s="6" t="n"/>
-      <c r="Y18" s="6" t="n"/>
-      <c r="Z18" s="6" t="n"/>
-      <c r="AA18" s="6" t="n"/>
+      <c r="X18" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y18" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z18" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA18" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB18" s="6" t="n"/>
       <c r="AC18" s="6" t="n"/>
       <c r="AD18" s="6" t="n"/>
@@ -2352,32 +2576,88 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2207A04</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>2207004</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
+      <c r="J19" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="n"/>
       <c r="N19" s="6" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="6" t="n"/>
+      <c r="O19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R19" s="6" t="n"/>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
-      <c r="X19" s="6" t="n"/>
-      <c r="Y19" s="6" t="n"/>
-      <c r="Z19" s="6" t="n"/>
-      <c r="AA19" s="6" t="n"/>
+      <c r="X19" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y19" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z19" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA19" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB19" s="6" t="n"/>
       <c r="AC19" s="6" t="n"/>
       <c r="AD19" s="6" t="n"/>
@@ -2402,32 +2682,88 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2207A04</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>2207004</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
+      <c r="J20" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n"/>
-      <c r="Q20" s="6" t="n"/>
+      <c r="O20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R20" s="6" t="n"/>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
-      <c r="X20" s="6" t="n"/>
-      <c r="Y20" s="6" t="n"/>
-      <c r="Z20" s="6" t="n"/>
-      <c r="AA20" s="6" t="n"/>
+      <c r="X20" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y20" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z20" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA20" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB20" s="6" t="n"/>
       <c r="AC20" s="6" t="n"/>
       <c r="AD20" s="6" t="n"/>
@@ -2452,32 +2788,88 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2207A04</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>2207004</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
+      <c r="J21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
+      <c r="O21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
-      <c r="X21" s="6" t="n"/>
-      <c r="Y21" s="6" t="n"/>
-      <c r="Z21" s="6" t="n"/>
-      <c r="AA21" s="6" t="n"/>
+      <c r="X21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z21" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA21" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB21" s="6" t="n"/>
       <c r="AC21" s="6" t="n"/>
       <c r="AD21" s="6" t="n"/>
@@ -2502,32 +2894,88 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2207A04</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>2207004</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
+      <c r="J22" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
+      <c r="O22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R22" s="6" t="n"/>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
-      <c r="AA22" s="6" t="n"/>
+      <c r="X22" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y22" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z22" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA22" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB22" s="6" t="n"/>
       <c r="AC22" s="6" t="n"/>
       <c r="AD22" s="6" t="n"/>
@@ -2550,6 +2998,1206 @@
       <c r="AU22" s="6" t="n"/>
       <c r="AV22" s="6" t="n"/>
     </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2207A10</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2207010</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>15</v>
+      </c>
+      <c r="K23" t="n">
+        <v>66</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>999</v>
+      </c>
+      <c r="P23" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2207A10</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2207010</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>15</v>
+      </c>
+      <c r="K24" t="n">
+        <v>69</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>999</v>
+      </c>
+      <c r="P24" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2207A10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2207010</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>15</v>
+      </c>
+      <c r="K25" t="n">
+        <v>66</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>999</v>
+      </c>
+      <c r="P25" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2207A10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2207010</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>15</v>
+      </c>
+      <c r="K26" t="n">
+        <v>69</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>999</v>
+      </c>
+      <c r="P26" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2207A10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2207010</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>20</v>
+      </c>
+      <c r="K27" t="n">
+        <v>66</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>999</v>
+      </c>
+      <c r="P27" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2207A10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2207010</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>20</v>
+      </c>
+      <c r="K28" t="n">
+        <v>69</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>999</v>
+      </c>
+      <c r="P28" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2207A10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2207010</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>20</v>
+      </c>
+      <c r="K29" t="n">
+        <v>66</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>999</v>
+      </c>
+      <c r="P29" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2207A10</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2207010</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>20</v>
+      </c>
+      <c r="K30" t="n">
+        <v>69</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>999</v>
+      </c>
+      <c r="P30" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2207A11</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2207011</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>15</v>
+      </c>
+      <c r="K31" t="n">
+        <v>66</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>999</v>
+      </c>
+      <c r="P31" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2207A11</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2207011</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>15</v>
+      </c>
+      <c r="K32" t="n">
+        <v>69</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>999</v>
+      </c>
+      <c r="P32" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2207A11</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2207011</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>15</v>
+      </c>
+      <c r="K33" t="n">
+        <v>66</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>999</v>
+      </c>
+      <c r="P33" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2207A11</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2207011</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>15</v>
+      </c>
+      <c r="K34" t="n">
+        <v>69</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>999</v>
+      </c>
+      <c r="P34" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2207A11</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2207011</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>20</v>
+      </c>
+      <c r="K35" t="n">
+        <v>66</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>999</v>
+      </c>
+      <c r="P35" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2207A11</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2207011</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>20</v>
+      </c>
+      <c r="K36" t="n">
+        <v>69</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>999</v>
+      </c>
+      <c r="P36" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2207A11</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2207011</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>20</v>
+      </c>
+      <c r="K37" t="n">
+        <v>66</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>999</v>
+      </c>
+      <c r="P37" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2207A11</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2207011</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>20</v>
+      </c>
+      <c r="K38" t="n">
+        <v>69</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>999</v>
+      </c>
+      <c r="P38" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="L3:AV3"/>

--- a/output/upload/S00026_2207_제로백H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2207_제로백H종신보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV38"/>
+  <dimension ref="A1:AV22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1339,7 +1339,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J7" s="6" t="n">
         <v>15</v>
       </c>
@@ -1445,7 +1449,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="n">
         <v>15</v>
       </c>
@@ -1518,22 +1526,22 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2207A03</t>
+          <t>2207A04</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>2207003</t>
+          <t>2207004</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1551,9 +1559,13 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J9" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>66</v>
@@ -1583,10 +1595,10 @@
       <c r="V9" s="6" t="n"/>
       <c r="W9" s="6" t="n"/>
       <c r="X9" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y9" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z9" s="6" t="inlineStr">
         <is>
@@ -1624,22 +1636,22 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2207A03</t>
+          <t>2207A04</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>2207003</t>
+          <t>2207004</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1657,9 +1669,13 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J10" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>69</v>
@@ -1689,10 +1705,10 @@
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
       <c r="X10" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y10" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z10" s="6" t="inlineStr">
         <is>
@@ -1730,22 +1746,22 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2207A03</t>
+          <t>2207A10</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>2207003</t>
+          <t>2207010</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1763,9 +1779,13 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I11" s="6" t="n"/>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J11" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>66</v>
@@ -1795,10 +1815,10 @@
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
       <c r="X11" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y11" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
@@ -1836,22 +1856,22 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2207A03</t>
+          <t>2207A10</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>2207003</t>
+          <t>2207010</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1869,9 +1889,13 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J12" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>69</v>
@@ -1901,10 +1925,10 @@
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
       <c r="X12" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y12" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z12" s="6" t="inlineStr">
         <is>
@@ -1942,22 +1966,22 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2207A03</t>
+          <t>2207A11</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>2207003</t>
+          <t>2207011</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1975,7 +1999,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J13" s="6" t="n">
         <v>20</v>
       </c>
@@ -2048,22 +2076,22 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2207A03</t>
+          <t>2207A11</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>2207003</t>
+          <t>2207011</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 표준체</t>
+          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -2081,7 +2109,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J14" s="6" t="n">
         <v>20</v>
       </c>
@@ -2152,88 +2184,32 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2207A04</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>2207004</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="6" t="n"/>
       <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
-      <c r="X15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z15" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="X15" s="6" t="n"/>
+      <c r="Y15" s="6" t="n"/>
+      <c r="Z15" s="6" t="n"/>
+      <c r="AA15" s="6" t="n"/>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
       <c r="AD15" s="6" t="n"/>
@@ -2258,88 +2234,32 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>2207A04</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>2207004</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="6" t="n"/>
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
-      <c r="X16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z16" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="X16" s="6" t="n"/>
+      <c r="Y16" s="6" t="n"/>
+      <c r="Z16" s="6" t="n"/>
+      <c r="AA16" s="6" t="n"/>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
       <c r="AD16" s="6" t="n"/>
@@ -2364,88 +2284,32 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2207A04</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>2207004</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="6" t="n"/>
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y17" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z17" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="X17" s="6" t="n"/>
+      <c r="Y17" s="6" t="n"/>
+      <c r="Z17" s="6" t="n"/>
+      <c r="AA17" s="6" t="n"/>
       <c r="AB17" s="6" t="n"/>
       <c r="AC17" s="6" t="n"/>
       <c r="AD17" s="6" t="n"/>
@@ -2470,88 +2334,32 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2207A04</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>2207004</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="6" t="n"/>
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
-      <c r="X18" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y18" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z18" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="X18" s="6" t="n"/>
+      <c r="Y18" s="6" t="n"/>
+      <c r="Z18" s="6" t="n"/>
+      <c r="AA18" s="6" t="n"/>
       <c r="AB18" s="6" t="n"/>
       <c r="AC18" s="6" t="n"/>
       <c r="AD18" s="6" t="n"/>
@@ -2576,88 +2384,32 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2207A04</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>2207004</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
       <c r="M19" s="6" t="n"/>
       <c r="N19" s="6" t="n"/>
-      <c r="O19" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="n"/>
       <c r="R19" s="6" t="n"/>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
-      <c r="X19" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y19" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z19" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="X19" s="6" t="n"/>
+      <c r="Y19" s="6" t="n"/>
+      <c r="Z19" s="6" t="n"/>
+      <c r="AA19" s="6" t="n"/>
       <c r="AB19" s="6" t="n"/>
       <c r="AC19" s="6" t="n"/>
       <c r="AD19" s="6" t="n"/>
@@ -2682,88 +2434,32 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>2207A04</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>2207004</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n"/>
+      <c r="Q20" s="6" t="n"/>
       <c r="R20" s="6" t="n"/>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
-      <c r="X20" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y20" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z20" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="X20" s="6" t="n"/>
+      <c r="Y20" s="6" t="n"/>
+      <c r="Z20" s="6" t="n"/>
+      <c r="AA20" s="6" t="n"/>
       <c r="AB20" s="6" t="n"/>
       <c r="AC20" s="6" t="n"/>
       <c r="AD20" s="6" t="n"/>
@@ -2788,88 +2484,32 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2207A04</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>2207004</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="L21" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
       <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="6" t="n"/>
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
-      <c r="X21" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y21" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z21" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="X21" s="6" t="n"/>
+      <c r="Y21" s="6" t="n"/>
+      <c r="Z21" s="6" t="n"/>
+      <c r="AA21" s="6" t="n"/>
       <c r="AB21" s="6" t="n"/>
       <c r="AC21" s="6" t="n"/>
       <c r="AD21" s="6" t="n"/>
@@ -2894,88 +2534,32 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>2207A04</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>2207004</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ) 건강체</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="n"/>
       <c r="R22" s="6" t="n"/>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y22" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z22" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA22" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="X22" s="6" t="n"/>
+      <c r="Y22" s="6" t="n"/>
+      <c r="Z22" s="6" t="n"/>
+      <c r="AA22" s="6" t="n"/>
       <c r="AB22" s="6" t="n"/>
       <c r="AC22" s="6" t="n"/>
       <c r="AD22" s="6" t="n"/>
@@ -2998,1206 +2582,6 @@
       <c r="AU22" s="6" t="n"/>
       <c r="AV22" s="6" t="n"/>
     </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2207A10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2207010</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>15</v>
-      </c>
-      <c r="K23" t="n">
-        <v>66</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>999</v>
-      </c>
-      <c r="P23" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2207A10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2207010</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>15</v>
-      </c>
-      <c r="K24" t="n">
-        <v>69</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>999</v>
-      </c>
-      <c r="P24" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2207A10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2207010</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>15</v>
-      </c>
-      <c r="K25" t="n">
-        <v>66</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O25" t="n">
-        <v>999</v>
-      </c>
-      <c r="P25" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X25" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2207A10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2207010</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>15</v>
-      </c>
-      <c r="K26" t="n">
-        <v>69</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O26" t="n">
-        <v>999</v>
-      </c>
-      <c r="P26" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X26" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2207A10</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2207010</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>20</v>
-      </c>
-      <c r="K27" t="n">
-        <v>66</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O27" t="n">
-        <v>999</v>
-      </c>
-      <c r="P27" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2207A10</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2207010</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>20</v>
-      </c>
-      <c r="K28" t="n">
-        <v>69</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O28" t="n">
-        <v>999</v>
-      </c>
-      <c r="P28" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2207A10</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2207010</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>20</v>
-      </c>
-      <c r="K29" t="n">
-        <v>66</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O29" t="n">
-        <v>999</v>
-      </c>
-      <c r="P29" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X29" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2207A10</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2207010</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 표준체</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>20</v>
-      </c>
-      <c r="K30" t="n">
-        <v>69</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O30" t="n">
-        <v>999</v>
-      </c>
-      <c r="P30" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X30" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2207A11</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2207011</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>15</v>
-      </c>
-      <c r="K31" t="n">
-        <v>66</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>999</v>
-      </c>
-      <c r="P31" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2207A11</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2207011</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>15</v>
-      </c>
-      <c r="K32" t="n">
-        <v>69</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O32" t="n">
-        <v>999</v>
-      </c>
-      <c r="P32" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2207A11</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2207011</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>15</v>
-      </c>
-      <c r="K33" t="n">
-        <v>66</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O33" t="n">
-        <v>999</v>
-      </c>
-      <c r="P33" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X33" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2207A11</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2207011</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>15</v>
-      </c>
-      <c r="K34" t="n">
-        <v>69</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O34" t="n">
-        <v>999</v>
-      </c>
-      <c r="P34" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X34" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2207A11</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2207011</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>20</v>
-      </c>
-      <c r="K35" t="n">
-        <v>66</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O35" t="n">
-        <v>999</v>
-      </c>
-      <c r="P35" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2207A11</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2207011</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>20</v>
-      </c>
-      <c r="K36" t="n">
-        <v>69</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O36" t="n">
-        <v>999</v>
-      </c>
-      <c r="P36" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X36" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2207A11</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2207011</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>20</v>
-      </c>
-      <c r="K37" t="n">
-        <v>66</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O37" t="n">
-        <v>999</v>
-      </c>
-      <c r="P37" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X37" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2207A11</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2207011</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>한화생명 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ) 건강체</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>20</v>
-      </c>
-      <c r="K38" t="n">
-        <v>69</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O38" t="n">
-        <v>999</v>
-      </c>
-      <c r="P38" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="X38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="L3:AV3"/>
